--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>108032</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552159.3435732077</v>
+        <v>552159</v>
       </c>
       <c r="R2" t="n">
-        <v>6250101.309019213</v>
+        <v>6250101</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1998-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>98110</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552159.3435732077</v>
+        <v>552159</v>
       </c>
       <c r="R3" t="n">
-        <v>6250101.309019213</v>
+        <v>6250101</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1999-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110532</v>
+        <v>110541</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100412</v>
+        <v>100418</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110541</v>
+        <v>110546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100418</v>
+        <v>100419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110546</v>
+        <v>110574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100419</v>
+        <v>100446</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110574</v>
+        <v>110580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100446</v>
+        <v>100452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110580</v>
+        <v>110587</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100452</v>
+        <v>100459</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110587</v>
+        <v>110591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100459</v>
+        <v>100463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110591</v>
+        <v>110599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100463</v>
+        <v>100470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110602</v>
+        <v>110607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100473</v>
+        <v>100478</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110607</v>
+        <v>110615</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100478</v>
+        <v>100486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110615</v>
+        <v>110625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100486</v>
+        <v>100496</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 2063-2023 artfynd.xlsx
+++ b/artfynd/A 2063-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74038300</v>
       </c>
       <c r="B2" t="n">
-        <v>110625</v>
+        <v>111214</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74983327</v>
       </c>
       <c r="B3" t="n">
-        <v>100496</v>
+        <v>100958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
